--- a/datasets/dataset_cca.xlsx
+++ b/datasets/dataset_cca.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -431,64 +431,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>OSI</t>
+          <t>CBT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BEHAV</t>
+          <t>COGT</t>
         </is>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="G3">
-        <v>16.7</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Abikoff_2013</t>
+          <t>Virta_2010</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CBT</t>
+          <t>DESI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COGT</t>
+          <t>ATMX</t>
         </is>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F4">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Virta_2010</t>
+          <t>Spencer_2002</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATMX</t>
+          <t>MPH</t>
         </is>
       </c>
       <c r="C5">
@@ -510,13 +510,13 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="F5">
         <v>25</v>
       </c>
       <c r="G5">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -527,32 +527,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DESI</t>
+          <t>A2AGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="F6">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Spencer_2002</t>
+          <t>Taylor_2001</t>
         </is>
       </c>
     </row>
@@ -564,27 +564,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>MPH</t>
         </is>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <v>20</v>
       </c>
       <c r="E7">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Taylor_2001</t>
+          <t>Kurlan_2002, Palumbo_2008, TSSG_2002</t>
         </is>
       </c>
     </row>
@@ -596,59 +596,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>MPH_A2AGO</t>
         </is>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>20</v>
       </c>
       <c r="E8">
-        <v>141</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>100</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kurlan_2002, Palumbo_2008, TSSG_2002</t>
+          <t>Palumbo_2008, TSSG_2002</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A2AGO</t>
+          <t>AMPH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MPH_A2AGO</t>
+          <t>ATMX</t>
         </is>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>4.7</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>4.5</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Palumbo_2008, TSSG_2002</t>
+          <t>Adler_2008, Kay_2009</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATMX</t>
+          <t>DASOT</t>
         </is>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>43</v>
       </c>
       <c r="E10">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Adler_2008, Kay_2009</t>
+          <t>Adler_2021</t>
         </is>
       </c>
     </row>
@@ -692,27 +692,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DASOT</t>
+          <t>MPH</t>
         </is>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>43</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="F11">
-        <v>2.3</v>
+        <v>11.6</v>
       </c>
       <c r="G11">
-        <v>20</v>
+        <v>3.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Adler_2021</t>
+          <t>Coghill_2013, Manos_1999, NCT01552902_NA, Plizka_2000, Ramtvedt_2013</t>
         </is>
       </c>
     </row>
@@ -724,98 +724,98 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>MODAF</t>
         </is>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>43</v>
       </c>
       <c r="E12">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>11.6</v>
+        <v>2.3</v>
       </c>
       <c r="G12">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Coghill_2013, Manos_1999, NCT01552902_NA, Plizka_2000, Ramtvedt_2013</t>
+          <t>Taylor_2000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ZINC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MODAF</t>
+          <t>PUFA</t>
         </is>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E13">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>2.3</v>
+        <v>16.7</v>
       </c>
       <c r="G13">
-        <v>12.5</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Taylor_2000</t>
+          <t>Salehi_2016</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZINC</t>
+          <t>ATMX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PUFA</t>
+          <t>MPH</t>
         </is>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="F14">
-        <v>16.7</v>
+        <v>9.1</v>
       </c>
       <c r="G14">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Salehi_2016</t>
+          <t>Adler_2009, Newcorn_2008, Spencer_2002, Weisler_2012</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ATMX</t>
+          <t>BUPR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -824,55 +824,55 @@
         </is>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>141</v>
       </c>
       <c r="F15">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Adler_2009, Newcorn_2008, Spencer_2002, Weisler_2012</t>
+          <t>Kuperman_2001</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BUPR</t>
+          <t>MPH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>PUFA</t>
         </is>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="E16">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="G16">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kuperman_2001</t>
+          <t>Barragan_2017</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PUFA</t>
+          <t>DBT</t>
         </is>
       </c>
       <c r="C17">
@@ -894,17 +894,17 @@
         <v>141</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>0.7</v>
       </c>
       <c r="G17">
-        <v>3.6</v>
+        <v>33.3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Barragan_2017</t>
+          <t>Philipsen_2015</t>
         </is>
       </c>
     </row>
@@ -916,121 +916,89 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DBT</t>
+          <t>MPH_A2AGO</t>
         </is>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>141</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G18">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Philipsen_2015</t>
+          <t>Palumbo_2008, TSSG_2002</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>COGT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MPH_A2AGO</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F19">
-        <v>1.4</v>
+        <v>10.7</v>
       </c>
       <c r="G19">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Palumbo_2008, TSSG_2002</t>
+          <t>Hasslinger_2021, Hasslinger_2022, Steiner_2014</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>COGT</t>
+          <t>PMI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>BEHAV</t>
         </is>
       </c>
       <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>33</v>
+      </c>
+      <c r="E20">
+        <v>5</v>
+      </c>
+      <c r="F20">
         <v>3</v>
       </c>
-      <c r="D20">
-        <v>28</v>
-      </c>
-      <c r="E20">
-        <v>36</v>
-      </c>
-      <c r="F20">
-        <v>10.7</v>
-      </c>
       <c r="G20">
-        <v>8.300000000000001</v>
+        <v>20</v>
       </c>
       <c r="H20" t="inlineStr">
-        <is>
-          <t>Hasslinger_2021, Hasslinger_2022, Steiner_2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>PMI</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BEHAV</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21">
-        <v>33</v>
-      </c>
-      <c r="E21">
-        <v>6</v>
-      </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21">
-        <v>16.7</v>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t>Pfiffner_2014</t>
         </is>
